--- a/artfynd/A 15427-2026 artfynd.xlsx
+++ b/artfynd/A 15427-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130185337</v>
+        <v>130185330</v>
       </c>
       <c r="B2" t="n">
-        <v>97828</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>843129</v>
+        <v>843049</v>
       </c>
       <c r="R2" t="n">
-        <v>7335257</v>
+        <v>7335196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -784,6 +784,454 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130185333</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Haparanda-Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>843042</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7335218</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130185334</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Haparanda-Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>843044</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7335220</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130185335</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Haparanda-Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>843048</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7335219</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130185337</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Haparanda-Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>843129</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7335257</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
